--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Alcaldía Local De Teusaquillo.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Alcaldía Local De Teusaquillo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Downloads/IIP - Esteban/bucle p35/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{030C8B2F-81C7-4042-BEF2-8E1343872D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3189E75-FBCD-644D-AAD2-7411FAD987F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{DE4E8B4B-5B23-447F-8CAE-CAA98A9197A7}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="19420" windowHeight="10300" xr2:uid="{DE4E8B4B-5B23-447F-8CAE-CAA98A9197A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -121,11 +121,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -550,9 +552,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BEFC64-6F0E-4814-BB8D-D4C4279029CC}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:P2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -602,7 +604,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="212.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="238" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>16</v>
       </c>
@@ -622,31 +624,31 @@
         <v>21</v>
       </c>
       <c r="G2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="K2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>24</v>
       </c>
       <c r="M2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="O2" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P2" s="4"/>
     </row>
